--- a/2083_2084/estimate/budget maag estimate/Goth/Goth jaleko.xlsx
+++ b/2083_2084/estimate/budget maag estimate/Goth/Goth jaleko.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA6159B-91A3-4646-9AE3-731F0ED983D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3B557A-A136-47DC-BD26-EE72F213366E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784" localSheetId="1">#REF!</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">WCR!$A$1:$K$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$12</definedName>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -163,21 +163,6 @@
     <t>sqm</t>
   </si>
   <si>
-    <t>-13% VAT for sheet</t>
-  </si>
-  <si>
-    <t>-13% VAT for nut bolt</t>
-  </si>
-  <si>
-    <t>-13% VAT for j-hook</t>
-  </si>
-  <si>
-    <t>-13% VAT for bitumen washer</t>
-  </si>
-  <si>
-    <t>Date:2082/09/07</t>
-  </si>
-  <si>
     <t>Location:- Shankharapur Municipality 1</t>
   </si>
   <si>
@@ -230,6 +215,9 @@
   </si>
   <si>
     <t>Project:- जलेको गोठ नयाँ बनाउने कार्य</t>
+  </si>
+  <si>
+    <t>Date:2083/04/26</t>
   </si>
 </sst>
 </file>
@@ -615,6 +603,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -624,6 +615,12 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -636,14 +633,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="43" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -661,27 +670,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1254,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
@@ -1273,100 +1261,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
+      <c r="A6" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="67" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
+      <c r="H6" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
@@ -1374,12 +1362,12 @@
       <c r="E7" s="58"/>
       <c r="F7" s="58"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="68" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
+      <c r="H7" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -1421,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
@@ -1451,7 +1439,7 @@
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="33">
-        <f t="shared" ref="G10" si="0">PRODUCT(C10:F10)</f>
+        <f t="shared" ref="G10:G11" si="0">PRODUCT(C10:F10)</f>
         <v>145</v>
       </c>
       <c r="H10" s="7"/>
@@ -1461,52 +1449,54 @@
     </row>
     <row r="11" spans="1:11" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="37"/>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="33">
+        <f t="shared" si="0"/>
+        <v>8.1000000000000014</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="36">
-        <f>SUM(G10:G10)</f>
-        <v>145</v>
-      </c>
-      <c r="H11" s="7" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="36">
+        <f>SUM(G10:G11)</f>
+        <v>153.1</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I12" s="6">
         <v>1092.46</v>
       </c>
-      <c r="J11" s="36">
-        <f>G11*I11</f>
-        <v>158406.70000000001</v>
-      </c>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="18">
-        <f>0.13*G11*6674.66/10</f>
-        <v>12581.7341</v>
-      </c>
-      <c r="K12" s="17"/>
+      <c r="J12" s="36">
+        <f>G12*I12</f>
+        <v>167255.62599999999</v>
+      </c>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
-      <c r="B13" s="32" t="s">
-        <v>29</v>
-      </c>
+      <c r="B13" s="32"/>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
@@ -1514,231 +1504,171 @@
       <c r="G13" s="17"/>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
-      <c r="J13" s="18">
-        <f>0.13*G11*1023.75/10</f>
-        <v>1929.76875</v>
-      </c>
+      <c r="J13" s="18"/>
       <c r="K13" s="17"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="18">
-        <f>0.13*G11*348.21/10</f>
-        <v>656.37585000000001</v>
-      </c>
-      <c r="K14" s="17"/>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="7">
+        <f t="shared" ref="G14" si="1">PRODUCT(C14:F14)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="6">
+        <v>500</v>
+      </c>
+      <c r="J14" s="7">
+        <f>G14*I14</f>
+        <v>500</v>
+      </c>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="18">
-        <f>0.13*G11*165/10</f>
-        <v>311.02500000000003</v>
-      </c>
-      <c r="K15" s="17"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="17"/>
-    </row>
-    <row r="17" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>2</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="7">
-        <f t="shared" ref="G17" si="1">PRODUCT(C17:F17)</f>
-        <v>1</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="6">
-        <v>500</v>
-      </c>
-      <c r="J17" s="7">
-        <f>G17*I17</f>
-        <v>500</v>
-      </c>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="5"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18">
+        <f>SUM(J10:J14)</f>
+        <v>167755.62599999999</v>
+      </c>
+      <c r="K16" s="25"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+    </row>
+    <row r="18" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="56">
+        <f>J16</f>
+        <v>167755.62599999999</v>
+      </c>
+      <c r="D18" s="57"/>
+      <c r="E18" s="9">
+        <v>100</v>
+      </c>
+      <c r="F18" s="26"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="31"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
-      <c r="B19" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18">
-        <f>SUM(J10:J17)</f>
-        <v>174385.60370000001</v>
-      </c>
-      <c r="K19" s="25"/>
+      <c r="B19" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="60">
+        <v>150000</v>
+      </c>
+      <c r="D19" s="61"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-    </row>
-    <row r="21" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26"/>
+      <c r="B20" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="60">
+        <f>C19-C22-C23</f>
+        <v>142500</v>
+      </c>
+      <c r="D20" s="61"/>
+      <c r="E20" s="9">
+        <f>C20/C18*100</f>
+        <v>84.94499016086651</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="56">
-        <f>J19</f>
-        <v>174385.60370000001</v>
-      </c>
-      <c r="D21" s="57"/>
+        <v>24</v>
+      </c>
+      <c r="C21" s="62">
+        <f>C18-C20</f>
+        <v>25255.625999999989</v>
+      </c>
+      <c r="D21" s="62"/>
       <c r="E21" s="9">
-        <v>100</v>
-      </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="31"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
+        <f>100-E20</f>
+        <v>15.05500983913349</v>
+      </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B22" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="59">
-        <v>150000</v>
-      </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="C22" s="56">
+        <f>C19*0.03</f>
+        <v>4500</v>
+      </c>
+      <c r="D22" s="57"/>
+      <c r="E22" s="9">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B23" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="59">
-        <f>C22-C25-C26</f>
-        <v>142500</v>
-      </c>
-      <c r="D23" s="60"/>
+        <v>23</v>
+      </c>
+      <c r="C23" s="56">
+        <f>C19*0.02</f>
+        <v>3000</v>
+      </c>
+      <c r="D23" s="57"/>
       <c r="E23" s="9">
-        <f>C23/C21*100</f>
-        <v>81.715461010844891</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B24" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="61">
-        <f>C21-C23</f>
-        <v>31885.603700000007</v>
-      </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="9">
-        <f>100-E23</f>
-        <v>18.284538989155109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B25" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="56">
-        <f>C22*0.03</f>
-        <v>4500</v>
-      </c>
-      <c r="D25" s="57"/>
-      <c r="E25" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B26" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="56">
-        <f>C22*0.02</f>
-        <v>3000</v>
-      </c>
-      <c r="D26" s="57"/>
-      <c r="E26" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -1746,6 +1676,14 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -1775,182 +1713,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="3" spans="1:13" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
     </row>
     <row r="4" spans="1:13" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
     </row>
     <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
+      <c r="A5" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
     </row>
     <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B6" s="38"/>
-      <c r="C6" s="69" t="e">
+      <c r="C6" s="76" t="e">
         <f>F49</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="70"/>
+      <c r="D6" s="77"/>
       <c r="E6" s="39"/>
       <c r="F6" s="38"/>
       <c r="G6" s="38"/>
       <c r="H6" s="38" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I6" s="38"/>
-      <c r="J6" s="69" t="e">
+      <c r="J6" s="76" t="e">
         <f>I49</f>
         <v>#REF!</v>
       </c>
-      <c r="K6" s="70"/>
+      <c r="K6" s="77"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="I7" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="I7" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
     </row>
     <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="66" t="str">
+      <c r="A8" s="63" t="str">
         <f>estimate!A6</f>
         <v>Project:- जलेको गोठ नयाँ बनाउने कार्य</v>
       </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="I8" s="77" t="s">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="I8" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="I9" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="74"/>
+      <c r="K9" s="74"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="70" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="70" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="I9" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="80" t="s">
+      <c r="K11" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="80" t="s">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="70"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="41" t="s">
         <v>41</v>
-      </c>
-      <c r="C11" s="80" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="81" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="80" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11" s="79" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="80"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="41" t="s">
-        <v>46</v>
       </c>
       <c r="E12" s="41" t="s">
         <v>13</v>
@@ -1959,7 +1897,7 @@
         <v>14</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H12" s="41" t="s">
         <v>13</v>
@@ -1967,10 +1905,10 @@
       <c r="I12" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="80"/>
-      <c r="K12" s="79"/>
-    </row>
-    <row r="13" spans="1:13" s="34" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="J12" s="70"/>
+      <c r="K12" s="69"/>
+    </row>
+    <row r="13" spans="1:13" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="e">
         <f>estimate!#REF!</f>
         <v>#REF!</v>
@@ -2069,20 +2007,20 @@
         <v xml:space="preserve">).#^ lblv ).$ dL.dL.afSnf] sf]?u]6]8 /+lug ss{6 kftfsf] 5fgf 5fpg] sfd </v>
       </c>
       <c r="C16" s="43" t="str">
-        <f>estimate!H11</f>
+        <f>estimate!H12</f>
         <v>sqm</v>
       </c>
       <c r="D16" s="43">
-        <f>estimate!G11</f>
-        <v>145</v>
+        <f>estimate!G12</f>
+        <v>153.1</v>
       </c>
       <c r="E16" s="43">
-        <f>estimate!I11</f>
+        <f>estimate!I12</f>
         <v>1092.46</v>
       </c>
       <c r="F16" s="43">
         <f>D16*E16</f>
-        <v>158406.70000000001</v>
+        <v>167255.62599999999</v>
       </c>
       <c r="G16" s="43" t="e">
         <f>#REF!</f>
@@ -2103,21 +2041,21 @@
       <c r="K16" s="45"/>
       <c r="M16" s="34">
         <f t="shared" ref="M16:M44" si="1">1.25*F16</f>
-        <v>198008.375</v>
+        <v>209069.53249999997</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="42"/>
-      <c r="B17" s="46" t="str">
-        <f>estimate!B12</f>
-        <v>-13% VAT for sheet</v>
+      <c r="B17" s="46" t="e">
+        <f>estimate!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
       <c r="E17" s="43"/>
-      <c r="F17" s="43">
-        <f>estimate!J12</f>
-        <v>12581.7341</v>
+      <c r="F17" s="43" t="e">
+        <f>estimate!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="G17" s="43"/>
       <c r="H17" s="43"/>
@@ -2130,23 +2068,23 @@
         <v>#REF!</v>
       </c>
       <c r="K17" s="45"/>
-      <c r="M17" s="34">
+      <c r="M17" s="34" t="e">
         <f t="shared" si="1"/>
-        <v>15727.167625</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="42"/>
-      <c r="B18" s="46" t="str">
-        <f>estimate!B13</f>
-        <v>-13% VAT for nut bolt</v>
+      <c r="B18" s="46" t="e">
+        <f>estimate!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
       <c r="E18" s="43"/>
-      <c r="F18" s="43">
-        <f>estimate!J13</f>
-        <v>1929.76875</v>
+      <c r="F18" s="43" t="e">
+        <f>estimate!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="G18" s="43"/>
       <c r="H18" s="43"/>
@@ -2162,16 +2100,16 @@
     </row>
     <row r="19" spans="1:13" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="42"/>
-      <c r="B19" s="46" t="str">
-        <f>estimate!B14</f>
-        <v>-13% VAT for j-hook</v>
+      <c r="B19" s="46" t="e">
+        <f>estimate!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
       <c r="E19" s="43"/>
-      <c r="F19" s="43">
-        <f>estimate!J14</f>
-        <v>656.37585000000001</v>
+      <c r="F19" s="43" t="e">
+        <f>estimate!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="G19" s="43"/>
       <c r="H19" s="43"/>
@@ -2187,16 +2125,16 @@
     </row>
     <row r="20" spans="1:13" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="42"/>
-      <c r="B20" s="46" t="str">
-        <f>estimate!B15</f>
-        <v>-13% VAT for bitumen washer</v>
+      <c r="B20" s="46" t="e">
+        <f>estimate!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
       <c r="E20" s="43"/>
-      <c r="F20" s="43">
-        <f>estimate!J15</f>
-        <v>311.02500000000003</v>
+      <c r="F20" s="43" t="e">
+        <f>estimate!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="G20" s="43"/>
       <c r="H20" s="43"/>
@@ -2223,7 +2161,7 @@
       <c r="J21" s="44"/>
       <c r="K21" s="45"/>
     </row>
-    <row r="22" spans="1:13" s="34" customFormat="1" ht="126" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="e">
         <f>estimate!#REF!</f>
         <v>#REF!</v>
@@ -2312,7 +2250,7 @@
       <c r="J24" s="44"/>
       <c r="K24" s="45"/>
     </row>
-    <row r="25" spans="1:13" s="34" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="42" t="e">
         <f>estimate!#REF!</f>
         <v>#REF!</v>
@@ -2401,7 +2339,7 @@
       <c r="J27" s="44"/>
       <c r="K27" s="45"/>
     </row>
-    <row r="28" spans="1:13" s="34" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="42" t="e">
         <f>estimate!#REF!</f>
         <v>#REF!</v>
@@ -2590,7 +2528,7 @@
       <c r="J34" s="44"/>
       <c r="K34" s="45"/>
     </row>
-    <row r="35" spans="1:13" s="34" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="42" t="e">
         <f>estimate!#REF!</f>
         <v>#REF!</v>
@@ -2843,7 +2781,7 @@
       <c r="J43" s="44"/>
       <c r="K43" s="45"/>
     </row>
-    <row r="44" spans="1:13" s="34" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="42" t="e">
         <f>estimate!#REF!</f>
         <v>#REF!</v>
@@ -2927,23 +2865,23 @@
     </row>
     <row r="47" spans="1:13" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="42">
-        <f>estimate!A17</f>
+        <f>estimate!A14</f>
         <v>2</v>
       </c>
       <c r="B47" s="51" t="str">
-        <f>estimate!B17</f>
+        <f>estimate!B14</f>
         <v>Information board (सुचना पाटि)</v>
       </c>
       <c r="C47" s="43" t="str">
-        <f>estimate!H17</f>
+        <f>estimate!H14</f>
         <v>no.</v>
       </c>
       <c r="D47" s="43">
-        <f>estimate!G17</f>
+        <f>estimate!G14</f>
         <v>1</v>
       </c>
       <c r="E47" s="43">
-        <f>estimate!I17</f>
+        <f>estimate!I14</f>
         <v>500</v>
       </c>
       <c r="F47" s="43">
@@ -3007,6 +2945,19 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
@@ -3014,19 +2965,6 @@
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
